--- a/reportes/ventas_propias.xlsx
+++ b/reportes/ventas_propias.xlsx
@@ -625,7 +625,7 @@
         <v>257</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>1.49</v>
       </c>
       <c r="F2" t="n">
         <v>402</v>
@@ -684,7 +684,7 @@
         <v>257</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>1.49</v>
       </c>
       <c r="F3" t="n">
         <v>157</v>
@@ -743,7 +743,7 @@
         <v>257</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>11.2</v>
       </c>
       <c r="F4" t="n">
         <v>259</v>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>11.2</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>257</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>155</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>257</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="F6" t="n">
         <v>335</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.4</v>
+        <v>5.12</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>257</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>1.49</v>
       </c>
       <c r="F7" t="n">
         <v>258</v>
@@ -975,7 +975,7 @@
         <v>257</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="F8" t="n">
         <v>263</v>
@@ -1030,7 +1030,7 @@
         <v>257</v>
       </c>
       <c r="E9" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="F9" t="n">
         <v>270</v>
@@ -1089,7 +1089,7 @@
         <v>257</v>
       </c>
       <c r="E10" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="F10" t="n">
         <v>216</v>
@@ -1148,7 +1148,7 @@
         <v>257</v>
       </c>
       <c r="E11" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="F11" t="n">
         <v>215</v>
@@ -1207,7 +1207,7 @@
         <v>259</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>339</v>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
         <v>259</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>1.49</v>
       </c>
       <c r="F13" t="n">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1325,7 +1325,7 @@
         <v>259</v>
       </c>
       <c r="E14" t="n">
-        <v>2.99</v>
+        <v>2.39</v>
       </c>
       <c r="F14" t="n">
         <v>165</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="O14" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>259</v>
       </c>
       <c r="E15" t="n">
-        <v>3.99</v>
+        <v>3.19</v>
       </c>
       <c r="F15" t="n">
         <v>499</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.19</v>
+        <v>2.55</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>260</v>
       </c>
       <c r="E16" t="n">
-        <v>3.99</v>
+        <v>3.19</v>
       </c>
       <c r="F16" t="n">
         <v>204</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.19</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>

--- a/reportes/ventas_propias.xlsx
+++ b/reportes/ventas_propias.xlsx
@@ -441,7 +441,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="E2" t="n">
         <v>1.5</v>
       </c>
       <c r="F2" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -667,31 +667,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbi1jb21tZXJjaWFsLWxp</t>
+          <t>Q3JlYXRpb24vd2FyZ2FtZS1tb3ZlbWVudC10cmF5cy0yNS0yOC01LTMyLTQwLW1tLXJvdW5kLWJhc2VzLW1hZ25ldC1yZWFkeS1tbWVyY2lhbA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween) | Commercial License</t>
+          <t>Wargame Movement Trays – 25, 28.5, 32 &amp; 40 mm Round Bases (Magnet Ready)mmercial License</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5004163</t>
+          <t>https://cults3d.com/:5036277</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="F3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
@@ -719,66 +719,1482 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+          <t>skirmish, regiment, squad, bambu, prusa, movement tray, wargame, tabletop, miniatures, 32mm base, 25mm base, 28mm, rpg, magnet, no supports, terrain, board game</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Q3JlYXRpb24vYmFuZGVqYXMtZGUtbW92aW1pZW50by1wYXJhLWp1ZWdvcy1kZS1ndWVycmEtYmFzZXMtcmVkb25kYXMtZGUtMjUtMjgtNS0zMi15LTQ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Wargame Movement Trays – 25, 28.5, 32 &amp; 40 mm Round Bases (Magnet Ready)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5036276</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>movement tray, wargame, tabletop, miniatures, 32mm base, 25mm base, 28mm, rpg, magnet, no supports, terrain, board game</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vY2FyLWN1cC1ob2xkZXItb3JnYW5pemVyLWluc2VydC1jb2lucy1jYXJkcy1hbmQtcGVucy02LXNpemVzLTY2LXRvLTgxLW1tLW1lLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Car Cup Holder Organizer Insert – Coins, Cards and Pens, 6 Sizes 66 to 81 mm (Measure First) | Commercial License</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5031209</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>car organizer, cup holder, car accessories, coin holder, card holder, pen holder, car console, interior organizer, cup holder insert, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vY2FyLWN1cC1ob2xkZXItb3JnYW5pemVyLWluc2VydC1jb2lucy1jYXJkcy1hbmQtcGVucy02LXNpemVzLTY2LXRvLTgxLW1tLW1l</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Car Cup Holder Organizer Insert – Coins, Cards and Pens, 6 Sizes 66 to 81 mm (Measure First)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5031208</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>car organizer, cup holder, car accessories, coin holder, card holder, pen holder, car console, interior organizer, cup holder insert, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vY29ybmVyLWJyYWNrZXQtd2l0aC1zaWRlLWd1c3NldHMtY291bnRlcnN1bmstbTMtbTQtbTUtNDAtdG8tMTAwLW1tLWNvbW1lcmM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Corner Bracket with Side Gussets – Countersunk, M3/M4/M5, 40 to 100 mm | Commercial License</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5030842</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>bracket, corner bracket, angle bracket, shelf bracket, gusset, hardware, woodworking, diy, workshop, countersunk, maker</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vY29ybmVyLWJyYWNrZXQtd2l0aC1zaWRlLWd1c3NldHMtY291bnRlcnN1bmstbTMtbTQtbTUtNDAtdG8tMTAwLW1t</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Corner Bracket with Side Gussets – Countersunk, M3/M4/M5, 40 to 100 mm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5030841</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>bracket, corner bracket, angle bracket, shelf bracket, gusset, hardware, woodworking, diy, workshop, countersunk, maker</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vZXYtY2hhcmdpbmctY2FibGUtbG9jay1jb2xsYXItOC1jYWJsZS1zaXplcy0xMi10by0yNi1tbS13aXRoLXBhZGxvY2stZXllcy12aXMtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EV Charging Cable Lock Collar – 8 Cable Sizes 12 to 26 mm with Padlock Eyes (Visible Deterrent) | Commercial License</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5030372</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F9" t="n">
+        <v>17</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ev charger, charging cable, cable lock, padlock, anti theft, cable clamp, electric car, home charging, wallbox, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vZXYtY2hhcmdpbmctY2FibGUtbG9jay1jb2xsYXItOC1jYWJsZS1zaXplcy0xMi10by0yNi1tbS13aXRoLXBhZGxvY2stZXllcy12aXM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EV Charging Cable Lock Collar – 8 Cable Sizes 12 to 26 mm with Padlock Eyes (Visible Deterrent)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5030358</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ev charger, charging cable, cable lock, padlock, anti theft, cable clamp, electric car, home charging, wallbox, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vZGVzay1zaWRlLXBvY2tldC1vcmdhbml6ZXItc2V0LXBob25lLXBlbnMtcmVtb3RlLWFuZC1rZXlzLWFkaGVzaXZlLXRhcGUtb3ItYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Desk Side Pocket Organizer Set – Phone, Pens, Remote and Keys (Adhesive Tape or Screw Mount) | Commercial License</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5024166</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>under desk organizer, desk organizer, wall pocket, phone holder, pen holder, remote holder, adhesive mount, desk accessory, cable organizer, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vZGVzay1zaWRlLXBvY2tldC1vcmdhbml6ZXItc2V0LXBob25lLXBlbnMtcmVtb3RlLWFuZC1rZXlzLWFkaGVzaXZlLXRhcGUtb3I</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Desk Side Pocket Organizer Set – Phone, Pens, Remote and Keys (Adhesive Tape or Screw Mount)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5024165</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>under desk organizer, desk organizer, wall pocket, phone holder, pen holder, remote holder, adhesive mount, desk accessory, cable organizer, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vdHdpc3RlZC1mYWNldGVkLXBsYW50ZXItZm9yLTktMTItMTUtY20tbnVyc2VyeS1wb3RzLWRyYWluYWdlLXNhdWNlci1jb20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Twisted Faceted Planter for 9, 12 &amp; 15 cm Nursery Pots – Drainage + Saucer | Commercial License</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5020606</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>home, planter, plant pot, succulent pot, flower pot, home decor, modern, geometric, drainage, saucer, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vdHdpc3RlZC1mYWNldGVkLXBsYW50ZXItZm9yLTktMTItMTUtY20tbnVyc2VyeS1wb3RzLWRyYWluYWdlLXNhdWNlcg</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Twisted Faceted Planter for 9, 12 &amp; 15 cm Nursery Pots – Drainage + Saucer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5020604</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>home, planter, plant pot, succulent pot, flower pot, home decor, modern, geometric, drainage, saucer, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vZGVzay1vcmdhbml6ZXItY2FkZHktcGVuLWN1cHMtcGhvbmUtc2xvdC1zdGlja3ktbm90ZS1wYWQtYnVzaW5lc3MtY2FyZC1ob2wtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Desk Organizer Caddy – Pen Cups, Phone Slot, Sticky Note Pad &amp; Business Card Holder | Commercial License</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5013777</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F15" t="n">
+        <v>19</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>desk organizer, pen holder, desk caddy, office, phone holder, sticky notes, business cards, desk accessory, no supports, stationery</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vZGVzay1vcmdhbml6ZXItY2FkZHktcGVuLWN1cHMtcGhvbmUtc2xvdC1zdGlja3ktbm90ZS1wYWQtYnVzaW5lc3MtY2FyZC1ob2w</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Desk Organizer Caddy – Pen Cups, Phone Slot, Sticky Note Pad &amp; Business Card Holder</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5013775</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>desk organizer, pen holder, desk caddy, office, phone holder, sticky notes, business cards, desk accessory, no supports, stationery</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vc29kYS1jYW4tbGlkLXNuYXAtb24tY292ZXItZm9yLXN0YW5kYXJkLXNsaW0tc2xlZWstY2Fucy13aXRoLXN0cmF3LWhvbGUtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Soda Can Lid – Snap-On Cover for Standard, Slim &amp; Sleek Cans, With Straw Hole | Commercial License</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5013380</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>can lid, can cover, soda can, beverage cover, drink cover, can topper, straw hole, no supports, picnic, camping</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vc29kYS1jYW4tbGlkLXNuYXAtb24tY292ZXItZm9yLXN0YW5kYXJkLXNsaW0tc2xlZWstY2Fucy13aXRoLXN0cmF3LWhvbGU</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Soda Can Lid – Snap-On Cover for Standard, Slim &amp; Sleek Cans, With Straw Hole</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5013379</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F18" t="n">
+        <v>17</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>can lid, can cover, soda can, beverage cover, drink cover, can topper, straw hole, no supports, picnic, camping</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vcGhvbmUtdGFibGV0LXN0YW5kLTMtdmlld2luZy1hbmdsZXMtY2FibGUtc2xvdC10aGljay1jYXNlLXZlcnNpb24tY29tbWVy</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Phone &amp; Tablet Stand – 3 Viewing Angles, Cable Slot, Thick Case Version | Commercial License</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5013062</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F19" t="n">
+        <v>25</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>accessory, phone stand, phone holder, tablet stand, desk setup, office, smartphone, charging stand, minimalist, no supports, desk accessory</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vcGhvbmUtdGFibGV0LXN0YW5kLTMtdmlld2luZy1hbmdsZXMtY2FibGUtc2xvdC10aGljay1jYXNlLXZlcnNpb24</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Phone &amp; Tablet Stand – 3 Viewing Angles, Cable Slot, Thick Case Version</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5013059</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="F20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>accessory, phone stand, phone holder, tablet stand, desk setup, office, smartphone, charging stand, minimalist, no supports, desk accessory</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vbWluaW1hbC1oZWFkcGhvbmUtc3RhbmQtMjMwLW1tLWNvbXBhY3QtcHJpbnRzLWZsYXQtbm8tc3VwcG9ydHMtY29tbWVyY2lh</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Minimal Headphone Stand – 230 mm &amp; Compact, Prints Flat, No Supports | Commercial License</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012946</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>headphone stand, headset holder, gaming, desk setup, minimalist, headphones, stand, no supports, gamer, office</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vbWluaW1hbC1oZWFkcGhvbmUtc3RhbmQtMjMwLW1tLWNvbXBhY3QtcHJpbnRzLWZsYXQtbm8tc3VwcG9ydHMtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Minimal Headphone Stand – 230 mm &amp; Compact, Prints Flat, No Supports</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012943</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F22" t="n">
+        <v>22</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>headphone stand, headset holder, gaming, desk setup, minimalist, headphones, stand, no supports, gamer, office</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vaGV4LWRlc2stb3JnYW5pemVyLW1vZHVsYXItaG9uZXljb21iLXBlbi1ob2xkZXItMS0zLTUtNy1jZWxscy1jb21tZXJjaQ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Hex Desk Organizer – Modular Honeycomb Pen Holder (1, 3, 5 &amp; 7 cells) | Commercial License</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012782</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F23" t="n">
+        <v>30</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>desk organizer, pen holder, honeycomb, hexagon, office, storage, minimalist, desk, organizer, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vaGV4LWRlc2stb3JnYW5pemVyLW1vZHVsYXItaG9uZXljb21iLXBlbi1ob2xkZXItMS0zLTUtNy1jZWxscw</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Hex Desk Organizer – Modular Honeycomb Pen Holder (1, 3, 5 &amp; 7 cells)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012781</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="F24" t="n">
+        <v>29</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>desk organizer, pen holder, honeycomb, hexagon, office, storage, minimalist, desk, organizer, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbi1jb21tZXJjaWFsLWxpLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween) | Commercial License</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012593</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F25" t="n">
+        <v>28</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbi1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012591</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F26" t="n">
+        <v>32</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbg</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>https://cults3d.com/:5004161</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F27" t="n">
+        <v>26</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vc25hcC1pbi1kZXNrLWNhYmxlLWNsaXBzLXRhcGUtbW91bnQtMS10by01LXNsb3Rz</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Snap-In Desk Cable Clips – Tape Mount, 1 to 5 Slots</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5015799</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>43</v>
+      </c>
+      <c r="G28" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="F4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>NUEVO</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Esperar: todavía no hay datos suficientes</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>GRATIS</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Imán de seguidores: 3 descargas</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>cable management, cable clip, desk setup, cable organizer, office, usb cable, charger, tape mount, no supports, gadget</t>
         </is>
       </c>
     </row>

--- a/reportes/ventas_propias.xlsx
+++ b/reportes/ventas_propias.xlsx
@@ -441,7 +441,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E2" t="n">
         <v>1.5</v>
       </c>
       <c r="F2" t="n">
-        <v>760</v>
+        <v>771</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -667,17 +667,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vd2FyZ2FtZS1tb3ZlbWVudC10cmF5cy0yNS0yOC01LTMyLTQwLW1tLXJvdW5kLWJhc2VzLW1hZ25ldC1yZWFkeS1tbWVyY2lhbA</t>
+          <t>Q3JlYXRpb24vdmVudGR1Y3RzLW1vZHVsYXItdHdpc3QtbG9jay1kdWN0LXN5c3RlbS0xMDAtMTI1LWFuZC0xNTAtbW0tNC01LTYtaW4tc3RyYS1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wargame Movement Trays – 25, 28.5, 32 &amp; 40 mm Round Bases (Magnet Ready)mmercial License</t>
+          <t>VentDucts Modular Twist-Lock Duct System – 100, 125 and 150 mm (4, 5, 6 in) Straight, Reducer and C | Commercial License</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5036277</t>
+          <t>https://cults3d.com/:5070195</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -687,10 +687,10 @@
         <v>9.99</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -719,34 +719,34 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>skirmish, regiment, squad, bambu, prusa, movement tray, wargame, tabletop, miniatures, 32mm base, 25mm base, 28mm, rpg, magnet, no supports, terrain, board game</t>
+          <t>duct, ventilation, bayonet, twist lock, grow tent, duct fan, modular, workshop, 3d printer enclosure, no supports</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vYmFuZGVqYXMtZGUtbW92aW1pZW50by1wYXJhLWp1ZWdvcy1kZS1ndWVycmEtYmFzZXMtcmVkb25kYXMtZGUtMjUtMjgtNS0zMi15LTQ</t>
+          <t>Q3JlYXRpb24vdmVudGR1Y3RzLW1vZHVsYXItdHdpc3QtbG9jay1kdWN0LXN5c3RlbS0xMDAtMTI1LWFuZC0xNTAtbW0tNC01LTYtaW4tc3RyYQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wargame Movement Trays – 25, 28.5, 32 &amp; 40 mm Round Bases (Magnet Ready)</t>
+          <t>VentDucts Modular Twist-Lock Duct System – 100, 125 and 150 mm (4, 5, 6 in) Straight, Reducer and Cap</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5036276</t>
+          <t>https://cults3d.com/:5070192</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2.79</v>
+        <v>5.62</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -774,28 +774,28 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.79</v>
+        <v>5.62</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>movement tray, wargame, tabletop, miniatures, 32mm base, 25mm base, 28mm, rpg, magnet, no supports, terrain, board game</t>
+          <t>duct, ventilation, bayonet, twist lock, grow tent, duct fan, modular, workshop, 3d printer enclosure, no supports</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vY2FyLWN1cC1ob2xkZXItb3JnYW5pemVyLWluc2VydC1jb2lucy1jYXJkcy1hbmQtcGVucy02LXNpemVzLTY2LXRvLTgxLW1tLW1lLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
+          <t>Q3JlYXRpb24vYW5pbWFsLWNhbi1jb3Zlci1wYWNrLWNhdC1mcm9nLWJhdC1iZWFyLXNvZGEtY2FuLWxpZHMtMy1jYW4tc2l6ZXMtbm8tc3VwLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Car Cup Holder Organizer Insert – Coins, Cards and Pens, 6 Sizes 66 to 81 mm (Measure First) | Commercial License</t>
+          <t>Animal Can Cover Pack – Cat, Frog, Bat &amp; Bear Soda Can Lids (3 Can Sizes, No Supports) | Commercial License</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5031209</t>
+          <t>https://cults3d.com/:5065472</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -805,7 +805,7 @@
         <v>9.99</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -837,34 +837,34 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>car organizer, cup holder, car accessories, coin holder, card holder, pen holder, car console, interior organizer, cup holder insert, no supports</t>
+          <t>can cover, can lid, soda can, beverage cover, can dust cover, reusable can protector, drink cover, cat, frog, bat, bear, party, picnic, no supports</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vY2FyLWN1cC1ob2xkZXItb3JnYW5pemVyLWluc2VydC1jb2lucy1jYXJkcy1hbmQtcGVucy02LXNpemVzLTY2LXRvLTgxLW1tLW1l</t>
+          <t>Q3JlYXRpb24vYW5pbWFsLWNhbi1jb3Zlci1wYWNrLWNhdC1mcm9nLWJhdC1iZWFyLXNvZGEtY2FuLWxpZHMtMy1jYW4tc2l6ZXMtbm8tc3Vw</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Car Cup Holder Organizer Insert – Coins, Cards and Pens, 6 Sizes 66 to 81 mm (Measure First)</t>
+          <t>Animal Can Cover Pack – Cat, Frog, Bat &amp; Bear Soda Can Lids (3 Can Sizes, No Supports)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5031208</t>
+          <t>https://cults3d.com/:5065471</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -892,38 +892,38 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>car organizer, cup holder, car accessories, coin holder, card holder, pen holder, car console, interior organizer, cup holder insert, no supports</t>
+          <t>can cover, can lid, soda can, beverage cover, can dust cover, reusable can protector, drink cover, cat, frog, bat, bear, party, picnic, no supports</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vY29ybmVyLWJyYWNrZXQtd2l0aC1zaWRlLWd1c3NldHMtY291bnRlcnN1bmstbTMtbTQtbTUtNDAtdG8tMTAwLW1tLWNvbW1lcmM</t>
+          <t>Q3JlYXRpb24vcGFzc2l2ZS1yYWRpYXRpb24tc2hpZWxkLWZvci13ZWF0aGVyLXN0YXRpb24tc2Vuc29ycy1sb3V2ZXItc3RhY2stZm9yLWRodDIyLWFuLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Corner Bracket with Side Gussets – Countersunk, M3/M4/M5, 40 to 100 mm | Commercial License</t>
+          <t>Passive Radiation Shield for Weather Station Sensors – Louver Stack for DHT22 and DS18B20 | Commercial License</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5030842</t>
+          <t>https://cults3d.com/:5055497</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>9.99</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -955,34 +955,34 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>bracket, corner bracket, angle bracket, shelf bracket, gusset, hardware, woodworking, diy, workshop, countersunk, maker</t>
+          <t>radiation shield, weather station, stevenson screen, solar shield, dht22, ds18b20, temperature sensor, esp32, agro iot, no supports</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vY29ybmVyLWJyYWNrZXQtd2l0aC1zaWRlLWd1c3NldHMtY291bnRlcnN1bmstbTMtbTQtbTUtNDAtdG8tMTAwLW1t</t>
+          <t>Q3JlYXRpb24vcGFzc2l2ZS1yYWRpYXRpb24tc2hpZWxkLWZvci13ZWF0aGVyLXN0YXRpb24tc2Vuc29ycy1sb3V2ZXItc3RhY2stZm9yLWRodDIyLWFu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Corner Bracket with Side Gussets – Countersunk, M3/M4/M5, 40 to 100 mm</t>
+          <t>Passive Radiation Shield for Weather Station Sensors – Louver Stack for DHT22 and DS18B20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5030841</t>
+          <t>https://cults3d.com/:5055491</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>1.67</v>
+        <v>3.37</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1010,38 +1010,38 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>3.37</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>bracket, corner bracket, angle bracket, shelf bracket, gusset, hardware, woodworking, diy, workshop, countersunk, maker</t>
+          <t>radiation shield, weather station, stevenson screen, solar shield, dht22, ds18b20, temperature sensor, esp32, agro iot, no supports</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZXYtY2hhcmdpbmctY2FibGUtbG9jay1jb2xsYXItOC1jYWJsZS1zaXplcy0xMi10by0yNi1tbS13aXRoLXBhZGxvY2stZXllcy12aXMtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+          <t>Q3JlYXRpb24vZXNwcmVzc28tZG9zaW5nLWZ1bm5lbC1mb3ItNTEtNTMtNTQtNTgtbW0tcG9ydGFmaWx0ZXJzLXdpZGUtaG9wcGVyLW5vLW1lcy1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EV Charging Cable Lock Collar – 8 Cable Sizes 12 to 26 mm with Padlock Eyes (Visible Deterrent) | Commercial License</t>
+          <t>Espresso Dosing Funnel for 51, 53, 54 &amp; 58 mm Portafilters – Wide Hopper, No Mess | Commercial License</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5030372</t>
+          <t>https://cults3d.com/:5050977</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>9.99</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1073,34 +1073,34 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ev charger, charging cable, cable lock, padlock, anti theft, cable clamp, electric car, home charging, wallbox, no supports</t>
+          <t>espresso, dosing funnel, portafilter, coffee, barista, 58mm, 54mm, 51mm, coffee accessories, no supports</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZXYtY2hhcmdpbmctY2FibGUtbG9jay1jb2xsYXItOC1jYWJsZS1zaXplcy0xMi10by0yNi1tbS13aXRoLXBhZGxvY2stZXllcy12aXM</t>
+          <t>Q3JlYXRpb24vZXNwcmVzc28tZG9zaW5nLWZ1bm5lbC1mb3ItNTEtNTMtNTQtNTgtbW0tcG9ydGFmaWx0ZXJzLXdpZGUtaG9wcGVyLW5vLW1lcw</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EV Charging Cable Lock Collar – 8 Cable Sizes 12 to 26 mm with Padlock Eyes (Visible Deterrent)</t>
+          <t>Espresso Dosing Funnel for 51, 53, 54 &amp; 58 mm Portafilters – Wide Hopper, No Mess</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5030358</t>
+          <t>https://cults3d.com/:5050975</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>2.79</v>
+        <v>1.68</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1128,38 +1128,38 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.79</v>
+        <v>1.68</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>ev charger, charging cable, cable lock, padlock, anti theft, cable clamp, electric car, home charging, wallbox, no supports</t>
+          <t>espresso, dosing funnel, portafilter, coffee, barista, 58mm, 54mm, 51mm, coffee accessories, no supports</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZGVzay1zaWRlLXBvY2tldC1vcmdhbml6ZXItc2V0LXBob25lLXBlbnMtcmVtb3RlLWFuZC1rZXlzLWFkaGVzaXZlLXRhcGUtb3ItYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+          <t>Q3JlYXRpb24vcG9ydGFibGUtYWMtZXhoYXVzdC1ob3NlLWFkYXB0ZXItc2V0LTEzMC1tbS0xNTAtbW0tYW5kLTQtaW4tZHJ5ZXItdmVudC1yZWR1Y2UtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Desk Side Pocket Organizer Set – Phone, Pens, Remote and Keys (Adhesive Tape or Screw Mount) | Commercial License</t>
+          <t>Portable AC Exhaust Hose Adapter Set – 130 mm, 150 mm and 4 in Dryer Vent Reducers and Couplers | Commercial License</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5024166</t>
+          <t>https://cults3d.com/:5050754</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>9.99</v>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1191,34 +1191,34 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>under desk organizer, desk organizer, wall pocket, phone holder, pen holder, remote holder, adhesive mount, desk accessory, cable organizer, no supports</t>
+          <t>portable air conditioner, ac hose adapter, exhaust hose, hose reducer, dryer vent, 130mm, 150mm, hose coupler, window kit, no supports</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZGVzay1zaWRlLXBvY2tldC1vcmdhbml6ZXItc2V0LXBob25lLXBlbnMtcmVtb3RlLWFuZC1rZXlzLWFkaGVzaXZlLXRhcGUtb3I</t>
+          <t>Q3JlYXRpb24vcG9ydGFibGUtYWMtZXhoYXVzdC1ob3NlLWFkYXB0ZXItc2V0LTEzMC1tbS0xNTAtbW0tYW5kLTQtaW4tZHJ5ZXItdmVudC1yZWR1Y2U</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Desk Side Pocket Organizer Set – Phone, Pens, Remote and Keys (Adhesive Tape or Screw Mount)</t>
+          <t>Portable AC Exhaust Hose Adapter Set – 130 mm, 150 mm and 4 in Dryer Vent Reducers and Couplers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5024165</t>
+          <t>https://cults3d.com/:5050750</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>2.79</v>
+        <v>2.24</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1246,41 +1246,41 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.79</v>
+        <v>2.24</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>under desk organizer, desk organizer, wall pocket, phone holder, pen holder, remote holder, adhesive mount, desk accessory, cable organizer, no supports</t>
+          <t>portable air conditioner, ac hose adapter, exhaust hose, hose reducer, dryer vent, 130mm, 150mm, hose coupler, window kit, no supports</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vdHdpc3RlZC1mYWNldGVkLXBsYW50ZXItZm9yLTktMTItMTUtY20tbnVyc2VyeS1wb3RzLWRyYWluYWdlLXNhdWNlci1jb20</t>
+          <t>Q3JlYXRpb24vd2FyZ2FtZS1tb3ZlbWVudC10cmF5cy0yNS0yOC01LTMyLTQwLW1tLXJvdW5kLWJhc2VzLW1hZ25ldC1yZWFkeS1tbWVyY2lhbA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Twisted Faceted Planter for 9, 12 &amp; 15 cm Nursery Pots – Drainage + Saucer | Commercial License</t>
+          <t>Wargame Movement Trays – 25, 28.5, 32 &amp; 40 mm Round Bases (Magnet Ready)mmercial License</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020606</t>
+          <t>https://cults3d.com/:5036277</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>9.99</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1309,34 +1309,34 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>home, planter, plant pot, succulent pot, flower pot, home decor, modern, geometric, drainage, saucer, no supports</t>
+          <t>skirmish, regiment, squad, bambu, prusa, movement tray, wargame, tabletop, miniatures, 32mm base, 25mm base, 28mm, rpg, magnet, no supports, terrain, board game</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vdHdpc3RlZC1mYWNldGVkLXBsYW50ZXItZm9yLTktMTItMTUtY20tbnVyc2VyeS1wb3RzLWRyYWluYWdlLXNhdWNlcg</t>
+          <t>Q3JlYXRpb24vYmFuZGVqYXMtZGUtbW92aW1pZW50by1wYXJhLWp1ZWdvcy1kZS1ndWVycmEtYmFzZXMtcmVkb25kYXMtZGUtMjUtMjgtNS0zMi15LTQ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Twisted Faceted Planter for 9, 12 &amp; 15 cm Nursery Pots – Drainage + Saucer</t>
+          <t>Wargame Movement Trays – 25, 28.5, 32 &amp; 40 mm Round Bases (Magnet Ready)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020604</t>
+          <t>https://cults3d.com/:5036276</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="F14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1364,38 +1364,38 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>home, planter, plant pot, succulent pot, flower pot, home decor, modern, geometric, drainage, saucer, no supports</t>
+          <t>movement tray, wargame, tabletop, miniatures, 32mm base, 25mm base, 28mm, rpg, magnet, no supports, terrain, board game</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZGVzay1vcmdhbml6ZXItY2FkZHktcGVuLWN1cHMtcGhvbmUtc2xvdC1zdGlja3ktbm90ZS1wYWQtYnVzaW5lc3MtY2FyZC1ob2wtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+          <t>Q3JlYXRpb24vY2FyLWN1cC1ob2xkZXItb3JnYW5pemVyLWluc2VydC1jb2lucy1jYXJkcy1hbmQtcGVucy02LXNpemVzLTY2LXRvLTgxLW1tLW1lLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Desk Organizer Caddy – Pen Cups, Phone Slot, Sticky Note Pad &amp; Business Card Holder | Commercial License</t>
+          <t>Car Cup Holder Organizer Insert – Coins, Cards and Pens, 6 Sizes 66 to 81 mm (Measure First) | Commercial License</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5013777</t>
+          <t>https://cults3d.com/:5031209</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>9.99</v>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1427,34 +1427,34 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>desk organizer, pen holder, desk caddy, office, phone holder, sticky notes, business cards, desk accessory, no supports, stationery</t>
+          <t>car organizer, cup holder, car accessories, coin holder, card holder, pen holder, car console, interior organizer, cup holder insert, no supports</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZGVzay1vcmdhbml6ZXItY2FkZHktcGVuLWN1cHMtcGhvbmUtc2xvdC1zdGlja3ktbm90ZS1wYWQtYnVzaW5lc3MtY2FyZC1ob2w</t>
+          <t>Q3JlYXRpb24vY2FyLWN1cC1ob2xkZXItb3JnYW5pemVyLWluc2VydC1jb2lucy1jYXJkcy1hbmQtcGVucy02LXNpemVzLTY2LXRvLTgxLW1tLW1l</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Desk Organizer Caddy – Pen Cups, Phone Slot, Sticky Note Pad &amp; Business Card Holder</t>
+          <t>Car Cup Holder Organizer Insert – Coins, Cards and Pens, 6 Sizes 66 to 81 mm (Measure First)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5013775</t>
+          <t>https://cults3d.com/:5031208</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1482,38 +1482,38 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>desk organizer, pen holder, desk caddy, office, phone holder, sticky notes, business cards, desk accessory, no supports, stationery</t>
+          <t>car organizer, cup holder, car accessories, coin holder, card holder, pen holder, car console, interior organizer, cup holder insert, no supports</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vc29kYS1jYW4tbGlkLXNuYXAtb24tY292ZXItZm9yLXN0YW5kYXJkLXNsaW0tc2xlZWstY2Fucy13aXRoLXN0cmF3LWhvbGUtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+          <t>Q3JlYXRpb24vY29ybmVyLWJyYWNrZXQtd2l0aC1zaWRlLWd1c3NldHMtY291bnRlcnN1bmstbTMtbTQtbTUtNDAtdG8tMTAwLW1tLWNvbW1lcmM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Soda Can Lid – Snap-On Cover for Standard, Slim &amp; Sleek Cans, With Straw Hole | Commercial License</t>
+          <t>Corner Bracket with Side Gussets – Countersunk, M3/M4/M5, 40 to 100 mm | Commercial License</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5013380</t>
+          <t>https://cults3d.com/:5030842</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>9.99</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1545,34 +1545,34 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>can lid, can cover, soda can, beverage cover, drink cover, can topper, straw hole, no supports, picnic, camping</t>
+          <t>bracket, corner bracket, angle bracket, shelf bracket, gusset, hardware, woodworking, diy, workshop, countersunk, maker</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vc29kYS1jYW4tbGlkLXNuYXAtb24tY292ZXItZm9yLXN0YW5kYXJkLXNsaW0tc2xlZWstY2Fucy13aXRoLXN0cmF3LWhvbGU</t>
+          <t>Q3JlYXRpb24vY29ybmVyLWJyYWNrZXQtd2l0aC1zaWRlLWd1c3NldHMtY291bnRlcnN1bmstbTMtbTQtbTUtNDAtdG8tMTAwLW1t</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Soda Can Lid – Snap-On Cover for Standard, Slim &amp; Sleek Cans, With Straw Hole</t>
+          <t>Corner Bracket with Side Gussets – Countersunk, M3/M4/M5, 40 to 100 mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5013379</t>
+          <t>https://cults3d.com/:5030841</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1600,38 +1600,38 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>can lid, can cover, soda can, beverage cover, drink cover, can topper, straw hole, no supports, picnic, camping</t>
+          <t>bracket, corner bracket, angle bracket, shelf bracket, gusset, hardware, woodworking, diy, workshop, countersunk, maker</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcGhvbmUtdGFibGV0LXN0YW5kLTMtdmlld2luZy1hbmdsZXMtY2FibGUtc2xvdC10aGljay1jYXNlLXZlcnNpb24tY29tbWVy</t>
+          <t>Q3JlYXRpb24vZXYtY2hhcmdpbmctY2FibGUtbG9jay1jb2xsYXItOC1jYWJsZS1zaXplcy0xMi10by0yNi1tbS13aXRoLXBhZGxvY2stZXllcy12aXMtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Phone &amp; Tablet Stand – 3 Viewing Angles, Cable Slot, Thick Case Version | Commercial License</t>
+          <t>EV Charging Cable Lock Collar – 8 Cable Sizes 12 to 26 mm with Padlock Eyes (Visible Deterrent) | Commercial License</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5013062</t>
+          <t>https://cults3d.com/:5030372</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>9.99</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1663,34 +1663,34 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>accessory, phone stand, phone holder, tablet stand, desk setup, office, smartphone, charging stand, minimalist, no supports, desk accessory</t>
+          <t>ev charger, charging cable, cable lock, padlock, anti theft, cable clamp, electric car, home charging, wallbox, no supports</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcGhvbmUtdGFibGV0LXN0YW5kLTMtdmlld2luZy1hbmdsZXMtY2FibGUtc2xvdC10aGljay1jYXNlLXZlcnNpb24</t>
+          <t>Q3JlYXRpb24vZXYtY2hhcmdpbmctY2FibGUtbG9jay1jb2xsYXItOC1jYWJsZS1zaXplcy0xMi10by0yNi1tbS13aXRoLXBhZGxvY2stZXllcy12aXM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Phone &amp; Tablet Stand – 3 Viewing Angles, Cable Slot, Thick Case Version</t>
+          <t>EV Charging Cable Lock Collar – 8 Cable Sizes 12 to 26 mm with Padlock Eyes (Visible Deterrent)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5013059</t>
+          <t>https://cults3d.com/:5030358</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1718,38 +1718,38 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>accessory, phone stand, phone holder, tablet stand, desk setup, office, smartphone, charging stand, minimalist, no supports, desk accessory</t>
+          <t>ev charger, charging cable, cable lock, padlock, anti theft, cable clamp, electric car, home charging, wallbox, no supports</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vbWluaW1hbC1oZWFkcGhvbmUtc3RhbmQtMjMwLW1tLWNvbXBhY3QtcHJpbnRzLWZsYXQtbm8tc3VwcG9ydHMtY29tbWVyY2lh</t>
+          <t>Q3JlYXRpb24vZGVzay1zaWRlLXBvY2tldC1vcmdhbml6ZXItc2V0LXBob25lLXBlbnMtcmVtb3RlLWFuZC1rZXlzLWFkaGVzaXZlLXRhcGUtb3ItYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Minimal Headphone Stand – 230 mm &amp; Compact, Prints Flat, No Supports | Commercial License</t>
+          <t>Desk Side Pocket Organizer Set – Phone, Pens, Remote and Keys (Adhesive Tape or Screw Mount) | Commercial License</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5012946</t>
+          <t>https://cults3d.com/:5024166</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
         <v>9.99</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1781,34 +1781,34 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>headphone stand, headset holder, gaming, desk setup, minimalist, headphones, stand, no supports, gamer, office</t>
+          <t>under desk organizer, desk organizer, wall pocket, phone holder, pen holder, remote holder, adhesive mount, desk accessory, cable organizer, no supports</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vbWluaW1hbC1oZWFkcGhvbmUtc3RhbmQtMjMwLW1tLWNvbXBhY3QtcHJpbnRzLWZsYXQtbm8tc3VwcG9ydHMtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+          <t>Q3JlYXRpb24vZGVzay1zaWRlLXBvY2tldC1vcmdhbml6ZXItc2V0LXBob25lLXBlbnMtcmVtb3RlLWFuZC1rZXlzLWFkaGVzaXZlLXRhcGUtb3I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Minimal Headphone Stand – 230 mm &amp; Compact, Prints Flat, No Supports</t>
+          <t>Desk Side Pocket Organizer Set – Phone, Pens, Remote and Keys (Adhesive Tape or Screw Mount)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5012943</t>
+          <t>https://cults3d.com/:5024165</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>1.99</v>
+        <v>2.8</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1836,38 +1836,38 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.99</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>headphone stand, headset holder, gaming, desk setup, minimalist, headphones, stand, no supports, gamer, office</t>
+          <t>under desk organizer, desk organizer, wall pocket, phone holder, pen holder, remote holder, adhesive mount, desk accessory, cable organizer, no supports</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vaGV4LWRlc2stb3JnYW5pemVyLW1vZHVsYXItaG9uZXljb21iLXBlbi1ob2xkZXItMS0zLTUtNy1jZWxscy1jb21tZXJjaQ</t>
+          <t>Q3JlYXRpb24vdHdpc3RlZC1mYWNldGVkLXBsYW50ZXItZm9yLTktMTItMTUtY20tbnVyc2VyeS1wb3RzLWRyYWluYWdlLXNhdWNlci1jb20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hex Desk Organizer – Modular Honeycomb Pen Holder (1, 3, 5 &amp; 7 cells) | Commercial License</t>
+          <t>Twisted Faceted Planter for 9, 12 &amp; 15 cm Nursery Pots – Drainage + Saucer | Commercial License</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5012782</t>
+          <t>https://cults3d.com/:5020606</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
         <v>9.99</v>
       </c>
       <c r="F23" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1899,34 +1899,34 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>desk organizer, pen holder, honeycomb, hexagon, office, storage, minimalist, desk, organizer, no supports</t>
+          <t>home, planter, plant pot, succulent pot, flower pot, home decor, modern, geometric, drainage, saucer, no supports</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vaGV4LWRlc2stb3JnYW5pemVyLW1vZHVsYXItaG9uZXljb21iLXBlbi1ob2xkZXItMS0zLTUtNy1jZWxscw</t>
+          <t>Q3JlYXRpb24vdHdpc3RlZC1mYWNldGVkLXBsYW50ZXItZm9yLTktMTItMTUtY20tbnVyc2VyeS1wb3RzLWRyYWluYWdlLXNhdWNlcg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hex Desk Organizer – Modular Honeycomb Pen Holder (1, 3, 5 &amp; 7 cells)</t>
+          <t>Twisted Faceted Planter for 9, 12 &amp; 15 cm Nursery Pots – Drainage + Saucer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5012781</t>
+          <t>https://cults3d.com/:5020604</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>2.49</v>
+        <v>2.83</v>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1954,38 +1954,38 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.49</v>
+        <v>2.83</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>desk organizer, pen holder, honeycomb, hexagon, office, storage, minimalist, desk, organizer, no supports</t>
+          <t>home, planter, plant pot, succulent pot, flower pot, home decor, modern, geometric, drainage, saucer, no supports</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbi1jb21tZXJjaWFsLWxpLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
+          <t>Q3JlYXRpb24vZGVzay1vcmdhbml6ZXItY2FkZHktcGVuLWN1cHMtcGhvbmUtc2xvdC1zdGlja3ktbm90ZS1wYWQtYnVzaW5lc3MtY2FyZC1ob2wtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween) | Commercial License</t>
+          <t>Desk Organizer Caddy – Pen Cups, Phone Slot, Sticky Note Pad &amp; Business Card Holder | Commercial License</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5012593</t>
+          <t>https://cults3d.com/:5013777</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E25" t="n">
         <v>9.99</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2017,34 +2017,34 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+          <t>desk organizer, pen holder, desk caddy, office, phone holder, sticky notes, business cards, desk accessory, no supports, stationery</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbi1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
+          <t>Q3JlYXRpb24vZGVzay1vcmdhbml6ZXItY2FkZHktcGVuLWN1cHMtcGhvbmUtc2xvdC1zdGlja3ktbm90ZS1wYWQtYnVzaW5lc3MtY2FyZC1ob2w</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween)</t>
+          <t>Desk Organizer Caddy – Pen Cups, Phone Slot, Sticky Note Pad &amp; Business Card Holder</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5012591</t>
+          <t>https://cults3d.com/:5013775</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E26" t="n">
-        <v>1.49</v>
+        <v>3.37</v>
       </c>
       <c r="F26" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2072,38 +2072,38 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.49</v>
+        <v>3.37</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+          <t>desk organizer, pen holder, desk caddy, office, phone holder, sticky notes, business cards, desk accessory, no supports, stationery</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbg</t>
+          <t>Q3JlYXRpb24vc29kYS1jYW4tbGlkLXNuYXAtb24tY292ZXItZm9yLXN0YW5kYXJkLXNsaW0tc2xlZWstY2Fucy13aXRoLXN0cmF3LWhvbGUtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween)</t>
+          <t>Soda Can Lid – Snap-On Cover for Standard, Slim &amp; Sleek Cans, With Straw Hole | Commercial License</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5004161</t>
+          <t>https://cults3d.com/:5013380</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
-        <v>1.49</v>
+        <v>9.99</v>
       </c>
       <c r="F27" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2131,68 +2131,658 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.49</v>
+        <v>9.99</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+          <t>can lid, can cover, soda can, beverage cover, drink cover, can topper, straw hole, no supports, picnic, camping</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Q3JlYXRpb24vc29kYS1jYW4tbGlkLXNuYXAtb24tY292ZXItZm9yLXN0YW5kYXJkLXNsaW0tc2xlZWstY2Fucy13aXRoLXN0cmF3LWhvbGU</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Soda Can Lid – Snap-On Cover for Standard, Slim &amp; Sleek Cans, With Straw Hole</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5013379</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F28" t="n">
+        <v>18</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>can lid, can cover, soda can, beverage cover, drink cover, can topper, straw hole, no supports, picnic, camping</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vcGhvbmUtdGFibGV0LXN0YW5kLTMtdmlld2luZy1hbmdsZXMtY2FibGUtc2xvdC10aGljay1jYXNlLXZlcnNpb24tY29tbWVy</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Phone &amp; Tablet Stand – 3 Viewing Angles, Cable Slot, Thick Case Version | Commercial License</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5013062</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F29" t="n">
+        <v>27</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>accessory, phone stand, phone holder, tablet stand, desk setup, office, smartphone, charging stand, minimalist, no supports, desk accessory</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vcGhvbmUtdGFibGV0LXN0YW5kLTMtdmlld2luZy1hbmdsZXMtY2FibGUtc2xvdC10aGljay1jYXNlLXZlcnNpb24</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Phone &amp; Tablet Stand – 3 Viewing Angles, Cable Slot, Thick Case Version</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5013059</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="F30" t="n">
+        <v>13</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>accessory, phone stand, phone holder, tablet stand, desk setup, office, smartphone, charging stand, minimalist, no supports, desk accessory</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vbWluaW1hbC1oZWFkcGhvbmUtc3RhbmQtMjMwLW1tLWNvbXBhY3QtcHJpbnRzLWZsYXQtbm8tc3VwcG9ydHMtY29tbWVyY2lh</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Minimal Headphone Stand – 230 mm &amp; Compact, Prints Flat, No Supports | Commercial License</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012946</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F31" t="n">
+        <v>34</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>headphone stand, headset holder, gaming, desk setup, minimalist, headphones, stand, no supports, gamer, office</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vbWluaW1hbC1oZWFkcGhvbmUtc3RhbmQtMjMwLW1tLWNvbXBhY3QtcHJpbnRzLWZsYXQtbm8tc3VwcG9ydHMtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Minimal Headphone Stand – 230 mm &amp; Compact, Prints Flat, No Supports</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012943</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F32" t="n">
+        <v>23</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>headphone stand, headset holder, gaming, desk setup, minimalist, headphones, stand, no supports, gamer, office</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vaGV4LWRlc2stb3JnYW5pemVyLW1vZHVsYXItaG9uZXljb21iLXBlbi1ob2xkZXItMS0zLTUtNy1jZWxscy1jb21tZXJjaQ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Hex Desk Organizer – Modular Honeycomb Pen Holder (1, 3, 5 &amp; 7 cells) | Commercial License</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012782</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F33" t="n">
+        <v>30</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>desk organizer, pen holder, honeycomb, hexagon, office, storage, minimalist, desk, organizer, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vaGV4LWRlc2stb3JnYW5pemVyLW1vZHVsYXItaG9uZXljb21iLXBlbi1ob2xkZXItMS0zLTUtNy1jZWxscw</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hex Desk Organizer – Modular Honeycomb Pen Holder (1, 3, 5 &amp; 7 cells)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012781</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="F34" t="n">
+        <v>29</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>desk organizer, pen holder, honeycomb, hexagon, office, storage, minimalist, desk, organizer, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbi1jb21tZXJjaWFsLWxpLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween) | Commercial License</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012593</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F35" t="n">
+        <v>29</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbi1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012591</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F36" t="n">
+        <v>33</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbg</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5004161</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>15</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F37" t="n">
+        <v>28</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Q3JlYXRpb24vc25hcC1pbi1kZXNrLWNhYmxlLWNsaXBzLXRhcGUtbW91bnQtMS10by01LXNsb3Rz</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Snap-In Desk Cable Clips – Tape Mount, 1 to 5 Slots</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>https://cults3d.com/:5015799</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>43</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="D38" t="n">
+        <v>13</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>57</v>
+      </c>
+      <c r="G38" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>GRATIS</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Imán de seguidores: 3 descargas</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Imán de seguidores: 4 descargas</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>cable management, cable clip, desk setup, cable organizer, office, usb cable, charger, tape mount, no supports, gadget</t>
         </is>

--- a/reportes/ventas_propias.xlsx
+++ b/reportes/ventas_propias.xlsx
@@ -441,7 +441,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.18</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,28 +622,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E2" t="n">
         <v>1.5</v>
       </c>
       <c r="F2" t="n">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.18</v>
+        <v>2.38</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0013</v>
+        <v>0.0026</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -667,27 +667,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vdmVudGR1Y3RzLW1vZHVsYXItdHdpc3QtbG9jay1kdWN0LXN5c3RlbS0xMDAtMTI1LWFuZC0xNTAtbW0tNC01LTYtaW4tc3RyYS1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
+          <t>Q3JlYXRpb24vZGljZS10b3dlci13aXRoLXJvbGxpbmctdHJheS0yLWFuZC0zLXJhbXAtdmVyc2lvbnMtZDIwLXNhZmUtZC1kLWFuZC1ib2FyZC1nYS1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VentDucts Modular Twist-Lock Duct System – 100, 125 and 150 mm (4, 5, 6 in) Straight, Reducer and C | Commercial License</t>
+          <t>Dice Tower with Rolling Tray – 2 and 3 Ramp Versions, d20-Safe, D&amp;D and Board Games | Commercial License</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5070195</t>
+          <t>https://cults3d.com/:5102517</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>9.99</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -719,34 +719,34 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>duct, ventilation, bayonet, twist lock, grow tent, duct fan, modular, workshop, 3d printer enclosure, no supports</t>
+          <t>dice tower, dice, dnd, rpg, tabletop, board game, pathfinder, rolling tray, gaming accessory, d20, wargame</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vdmVudGR1Y3RzLW1vZHVsYXItdHdpc3QtbG9jay1kdWN0LXN5c3RlbS0xMDAtMTI1LWFuZC0xNTAtbW0tNC01LTYtaW4tc3RyYQ</t>
+          <t>Q3JlYXRpb24vZGljZS10b3dlci13aXRoLXJvbGxpbmctdHJheS0yLWFuZC0zLXJhbXAtdmVyc2lvbnMtZDIwLXNhZmUtZC1kLWFuZC1ib2FyZC1nYQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VentDucts Modular Twist-Lock Duct System – 100, 125 and 150 mm (4, 5, 6 in) Straight, Reducer and Cap</t>
+          <t>Dice Tower with Rolling Tray – 2 and 3 Ramp Versions, d20-Safe, D&amp;D and Board Games</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5070192</t>
+          <t>https://cults3d.com/:5102516</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>5.62</v>
+        <v>5.61</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -774,28 +774,28 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.62</v>
+        <v>5.61</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>duct, ventilation, bayonet, twist lock, grow tent, duct fan, modular, workshop, 3d printer enclosure, no supports</t>
+          <t>dice tower, dice, dnd, rpg, tabletop, board game, pathfinder, rolling tray, gaming accessory, d20, wargame</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vYW5pbWFsLWNhbi1jb3Zlci1wYWNrLWNhdC1mcm9nLWJhdC1iZWFyLXNvZGEtY2FuLWxpZHMtMy1jYW4tc2l6ZXMtbm8tc3VwLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
+          <t>Q3JlYXRpb24vY2FyZC1kZWNrLWJveC1mb3Itc2xlZXZlZC1jYXJkcy10Y2ctMTAwLTYwLW1pbmktZXVyby10YXJvdC1zbnVnLWNhcC1uby1zLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Animal Can Cover Pack – Cat, Frog, Bat &amp; Bear Soda Can Lids (3 Can Sizes, No Supports) | Commercial License</t>
+          <t>Card Deck Box for Sleeved Cards – TCG 100 &amp; 60, Mini Euro, Tarot (Snug Cap, No Supports) | Commercial License</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5065472</t>
+          <t>https://cults3d.com/:5092021</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -805,7 +805,7 @@
         <v>9.99</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -837,34 +837,34 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>can cover, can lid, soda can, beverage cover, can dust cover, reusable can protector, drink cover, cat, frog, bat, bear, party, picnic, no supports</t>
+          <t>deck box, card box, tcg, mtg, commander, board game, tabletop, card storage, tarot, d&amp;d, sleeved cards, no supports</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vYW5pbWFsLWNhbi1jb3Zlci1wYWNrLWNhdC1mcm9nLWJhdC1iZWFyLXNvZGEtY2FuLWxpZHMtMy1jYW4tc2l6ZXMtbm8tc3Vw</t>
+          <t>Q3JlYXRpb24vY2FyZC1kZWNrLWJveC1mb3Itc2xlZXZlZC1jYXJkcy10Y2ctMTAwLTYwLW1pbmktZXVyby10YXJvdC1zbnVnLWNhcC1uby1z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Animal Can Cover Pack – Cat, Frog, Bat &amp; Bear Soda Can Lids (3 Can Sizes, No Supports)</t>
+          <t>Card Deck Box for Sleeved Cards – TCG 100 &amp; 60, Mini Euro, Tarot (Snug Cap, No Supports)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5065471</t>
+          <t>https://cults3d.com/:5092020</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>3.37</v>
+        <v>4.48</v>
       </c>
       <c r="F6" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -892,38 +892,38 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.37</v>
+        <v>4.48</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>can cover, can lid, soda can, beverage cover, can dust cover, reusable can protector, drink cover, cat, frog, bat, bear, party, picnic, no supports</t>
+          <t>deck box, card box, tcg, mtg, commander, board game, tabletop, card storage, tarot, d&amp;d, sleeved cards, no supports</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcGFzc2l2ZS1yYWRpYXRpb24tc2hpZWxkLWZvci13ZWF0aGVyLXN0YXRpb24tc2Vuc29ycy1sb3V2ZXItc3RhY2stZm9yLWRodDIyLWFuLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
+          <t>Q3JlYXRpb24vc2FtdXJhaS1oZWxtZXQtZGVzay1maWd1cmUta2FidXRvLXdpdGgtY3Jlc2NlbnQtY3Jlc3QtMy1zaXplcy1uby1zdXBwb3J0cy1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Passive Radiation Shield for Weather Station Sensors – Louver Stack for DHT22 and DS18B20 | Commercial License</t>
+          <t>Samurai Helmet Desk Figure – Kabuto with Crescent Crest (3 Sizes, No Supports) | Commercial License</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5055497</t>
+          <t>https://cults3d.com/:5086607</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>9.99</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -955,34 +955,34 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>radiation shield, weather station, stevenson screen, solar shield, dht22, ds18b20, temperature sensor, esp32, agro iot, no supports</t>
+          <t>samurai, kabuto, helmet, japan, desk decor, figure, bushido, warrior, home decor, shelf, original design</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcGFzc2l2ZS1yYWRpYXRpb24tc2hpZWxkLWZvci13ZWF0aGVyLXN0YXRpb24tc2Vuc29ycy1sb3V2ZXItc3RhY2stZm9yLWRodDIyLWFu</t>
+          <t>Q3JlYXRpb24vc2FtdXJhaS1oZWxtZXQtZGVzay1maWd1cmUta2FidXRvLXdpdGgtY3Jlc2NlbnQtY3Jlc3QtMy1zaXplcy1uby1zdXBwb3J0cw</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Passive Radiation Shield for Weather Station Sensors – Louver Stack for DHT22 and DS18B20</t>
+          <t>Samurai Helmet Desk Figure – Kabuto with Crescent Crest (3 Sizes, No Supports)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5055491</t>
+          <t>https://cults3d.com/:5086606</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>3.37</v>
+        <v>6.73</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1010,38 +1010,38 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.37</v>
+        <v>6.73</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>radiation shield, weather station, stevenson screen, solar shield, dht22, ds18b20, temperature sensor, esp32, agro iot, no supports</t>
+          <t>samurai, kabuto, helmet, japan, desk decor, figure, bushido, warrior, home decor, shelf, original design</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZXNwcmVzc28tZG9zaW5nLWZ1bm5lbC1mb3ItNTEtNTMtNTQtNTgtbW0tcG9ydGFmaWx0ZXJzLXdpZGUtaG9wcGVyLW5vLW1lcy1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
+          <t>Q3JlYXRpb24vdmVudGR1Y3RzLW1vZHVsYXItdHdpc3QtbG9jay1kdWN0LXN5c3RlbS0xMDAtMTI1LWFuZC0xNTAtbW0tNC01LTYtaW4tc3RyYS1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Espresso Dosing Funnel for 51, 53, 54 &amp; 58 mm Portafilters – Wide Hopper, No Mess | Commercial License</t>
+          <t>VentDucts Modular Twist-Lock Duct System – 100, 125 and 150 mm (4, 5, 6 in) Straight, Reducer and C | Commercial License</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5050977</t>
+          <t>https://cults3d.com/:5070195</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>9.99</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1073,34 +1073,34 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>espresso, dosing funnel, portafilter, coffee, barista, 58mm, 54mm, 51mm, coffee accessories, no supports</t>
+          <t>duct, ventilation, bayonet, twist lock, grow tent, duct fan, modular, workshop, 3d printer enclosure, no supports</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZXNwcmVzc28tZG9zaW5nLWZ1bm5lbC1mb3ItNTEtNTMtNTQtNTgtbW0tcG9ydGFmaWx0ZXJzLXdpZGUtaG9wcGVyLW5vLW1lcw</t>
+          <t>Q3JlYXRpb24vdmVudGR1Y3RzLW1vZHVsYXItdHdpc3QtbG9jay1kdWN0LXN5c3RlbS0xMDAtMTI1LWFuZC0xNTAtbW0tNC01LTYtaW4tc3RyYQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Espresso Dosing Funnel for 51, 53, 54 &amp; 58 mm Portafilters – Wide Hopper, No Mess</t>
+          <t>VentDucts Modular Twist-Lock Duct System – 100, 125 and 150 mm (4, 5, 6 in) Straight, Reducer and Cap</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5050975</t>
+          <t>https://cults3d.com/:5070192</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>1.68</v>
+        <v>5.61</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1128,38 +1128,38 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.68</v>
+        <v>5.61</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>espresso, dosing funnel, portafilter, coffee, barista, 58mm, 54mm, 51mm, coffee accessories, no supports</t>
+          <t>duct, ventilation, bayonet, twist lock, grow tent, duct fan, modular, workshop, 3d printer enclosure, no supports</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcG9ydGFibGUtYWMtZXhoYXVzdC1ob3NlLWFkYXB0ZXItc2V0LTEzMC1tbS0xNTAtbW0tYW5kLTQtaW4tZHJ5ZXItdmVudC1yZWR1Y2UtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+          <t>Q3JlYXRpb24vYW5pbWFsLWNhbi1jb3Zlci1wYWNrLWNhdC1mcm9nLWJhdC1iZWFyLXNvZGEtY2FuLWxpZHMtMy1jYW4tc2l6ZXMtbm8tc3VwLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Portable AC Exhaust Hose Adapter Set – 130 mm, 150 mm and 4 in Dryer Vent Reducers and Couplers | Commercial License</t>
+          <t>Animal Can Cover Pack – Cat, Frog, Bat &amp; Bear Soda Can Lids (3 Can Sizes, No Supports) | Commercial License</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5050754</t>
+          <t>https://cults3d.com/:5065472</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>9.99</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1191,34 +1191,34 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>portable air conditioner, ac hose adapter, exhaust hose, hose reducer, dryer vent, 130mm, 150mm, hose coupler, window kit, no supports</t>
+          <t>can cover, can lid, soda can, beverage cover, can dust cover, reusable can protector, drink cover, cat, frog, bat, bear, party, picnic, no supports</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcG9ydGFibGUtYWMtZXhoYXVzdC1ob3NlLWFkYXB0ZXItc2V0LTEzMC1tbS0xNTAtbW0tYW5kLTQtaW4tZHJ5ZXItdmVudC1yZWR1Y2U</t>
+          <t>Q3JlYXRpb24vYW5pbWFsLWNhbi1jb3Zlci1wYWNrLWNhdC1mcm9nLWJhdC1iZWFyLXNvZGEtY2FuLWxpZHMtMy1jYW4tc2l6ZXMtbm8tc3Vw</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Portable AC Exhaust Hose Adapter Set – 130 mm, 150 mm and 4 in Dryer Vent Reducers and Couplers</t>
+          <t>Animal Can Cover Pack – Cat, Frog, Bat &amp; Bear Soda Can Lids (3 Can Sizes, No Supports)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5050750</t>
+          <t>https://cults3d.com/:5065471</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>2.24</v>
+        <v>3.36</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1246,41 +1246,41 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.24</v>
+        <v>3.36</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>portable air conditioner, ac hose adapter, exhaust hose, hose reducer, dryer vent, 130mm, 150mm, hose coupler, window kit, no supports</t>
+          <t>can cover, can lid, soda can, beverage cover, can dust cover, reusable can protector, drink cover, cat, frog, bat, bear, party, picnic, no supports</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vd2FyZ2FtZS1tb3ZlbWVudC10cmF5cy0yNS0yOC01LTMyLTQwLW1tLXJvdW5kLWJhc2VzLW1hZ25ldC1yZWFkeS1tbWVyY2lhbA</t>
+          <t>Q3JlYXRpb24vcGFzc2l2ZS1yYWRpYXRpb24tc2hpZWxkLWZvci13ZWF0aGVyLXN0YXRpb24tc2Vuc29ycy1sb3V2ZXItc3RhY2stZm9yLWRodDIyLWFuLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wargame Movement Trays – 25, 28.5, 32 &amp; 40 mm Round Bases (Magnet Ready)mmercial License</t>
+          <t>Passive Radiation Shield for Weather Station Sensors – Louver Stack for DHT22 and DS18B20 | Commercial License</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5036277</t>
+          <t>https://cults3d.com/:5055497</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>9.99</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1309,35 +1309,35 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>skirmish, regiment, squad, bambu, prusa, movement tray, wargame, tabletop, miniatures, 32mm base, 25mm base, 28mm, rpg, magnet, no supports, terrain, board game</t>
+          <t>radiation shield, weather station, stevenson screen, solar shield, dht22, ds18b20, temperature sensor, esp32, agro iot, no supports</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vYmFuZGVqYXMtZGUtbW92aW1pZW50by1wYXJhLWp1ZWdvcy1kZS1ndWVycmEtYmFzZXMtcmVkb25kYXMtZGUtMjUtMjgtNS0zMi15LTQ</t>
+          <t>Q3JlYXRpb24vcGFzc2l2ZS1yYWRpYXRpb24tc2hpZWxkLWZvci13ZWF0aGVyLXN0YXRpb24tc2Vuc29ycy1sb3V2ZXItc3RhY2stZm9yLWRodDIyLWFu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wargame Movement Trays – 25, 28.5, 32 &amp; 40 mm Round Bases (Magnet Ready)</t>
+          <t>Passive Radiation Shield for Weather Station Sensors – Louver Stack for DHT22 and DS18B20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5036276</t>
+          <t>https://cults3d.com/:5055491</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="F14" t="n">
         <v>9</v>
       </c>
-      <c r="E14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F14" t="n">
-        <v>20</v>
-      </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
@@ -1364,38 +1364,38 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>3.36</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>movement tray, wargame, tabletop, miniatures, 32mm base, 25mm base, 28mm, rpg, magnet, no supports, terrain, board game</t>
+          <t>radiation shield, weather station, stevenson screen, solar shield, dht22, ds18b20, temperature sensor, esp32, agro iot, no supports</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vY2FyLWN1cC1ob2xkZXItb3JnYW5pemVyLWluc2VydC1jb2lucy1jYXJkcy1hbmQtcGVucy02LXNpemVzLTY2LXRvLTgxLW1tLW1lLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
+          <t>Q3JlYXRpb24vZXNwcmVzc28tZG9zaW5nLWZ1bm5lbC1mb3ItNTEtNTMtNTQtNTgtbW0tcG9ydGFmaWx0ZXJzLXdpZGUtaG9wcGVyLW5vLW1lcy1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Car Cup Holder Organizer Insert – Coins, Cards and Pens, 6 Sizes 66 to 81 mm (Measure First) | Commercial License</t>
+          <t>Espresso Dosing Funnel for 51, 53, 54 &amp; 58 mm Portafilters – Wide Hopper, No Mess | Commercial License</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5031209</t>
+          <t>https://cults3d.com/:5050977</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>9.99</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1427,34 +1427,34 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>car organizer, cup holder, car accessories, coin holder, card holder, pen holder, car console, interior organizer, cup holder insert, no supports</t>
+          <t>espresso, dosing funnel, portafilter, coffee, barista, 58mm, 54mm, 51mm, coffee accessories, no supports</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vY2FyLWN1cC1ob2xkZXItb3JnYW5pemVyLWluc2VydC1jb2lucy1jYXJkcy1hbmQtcGVucy02LXNpemVzLTY2LXRvLTgxLW1tLW1l</t>
+          <t>Q3JlYXRpb24vZXNwcmVzc28tZG9zaW5nLWZ1bm5lbC1mb3ItNTEtNTMtNTQtNTgtbW0tcG9ydGFmaWx0ZXJzLXdpZGUtaG9wcGVyLW5vLW1lcw</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Car Cup Holder Organizer Insert – Coins, Cards and Pens, 6 Sizes 66 to 81 mm (Measure First)</t>
+          <t>Espresso Dosing Funnel for 51, 53, 54 &amp; 58 mm Portafilters – Wide Hopper, No Mess</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5031208</t>
+          <t>https://cults3d.com/:5050975</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>3.37</v>
+        <v>1.67</v>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1482,38 +1482,38 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.37</v>
+        <v>1.67</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>car organizer, cup holder, car accessories, coin holder, card holder, pen holder, car console, interior organizer, cup holder insert, no supports</t>
+          <t>espresso, dosing funnel, portafilter, coffee, barista, 58mm, 54mm, 51mm, coffee accessories, no supports</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vY29ybmVyLWJyYWNrZXQtd2l0aC1zaWRlLWd1c3NldHMtY291bnRlcnN1bmstbTMtbTQtbTUtNDAtdG8tMTAwLW1tLWNvbW1lcmM</t>
+          <t>Q3JlYXRpb24vcG9ydGFibGUtYWMtZXhoYXVzdC1ob3NlLWFkYXB0ZXItc2V0LTEzMC1tbS0xNTAtbW0tYW5kLTQtaW4tZHJ5ZXItdmVudC1yZWR1Y2UtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Corner Bracket with Side Gussets – Countersunk, M3/M4/M5, 40 to 100 mm | Commercial License</t>
+          <t>Portable AC Exhaust Hose Adapter Set – 130 mm, 150 mm and 4 in Dryer Vent Reducers and Couplers | Commercial License</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5030842</t>
+          <t>https://cults3d.com/:5050754</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>9.99</v>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1545,34 +1545,34 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>bracket, corner bracket, angle bracket, shelf bracket, gusset, hardware, woodworking, diy, workshop, countersunk, maker</t>
+          <t>portable air conditioner, ac hose adapter, exhaust hose, hose reducer, dryer vent, 130mm, 150mm, hose coupler, window kit, no supports</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vY29ybmVyLWJyYWNrZXQtd2l0aC1zaWRlLWd1c3NldHMtY291bnRlcnN1bmstbTMtbTQtbTUtNDAtdG8tMTAwLW1t</t>
+          <t>Q3JlYXRpb24vcG9ydGFibGUtYWMtZXhoYXVzdC1ob3NlLWFkYXB0ZXItc2V0LTEzMC1tbS0xNTAtbW0tYW5kLTQtaW4tZHJ5ZXItdmVudC1yZWR1Y2U</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Corner Bracket with Side Gussets – Countersunk, M3/M4/M5, 40 to 100 mm</t>
+          <t>Portable AC Exhaust Hose Adapter Set – 130 mm, 150 mm and 4 in Dryer Vent Reducers and Couplers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5030841</t>
+          <t>https://cults3d.com/:5050750</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>1.68</v>
+        <v>2.24</v>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1600,41 +1600,41 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.68</v>
+        <v>2.24</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>bracket, corner bracket, angle bracket, shelf bracket, gusset, hardware, woodworking, diy, workshop, countersunk, maker</t>
+          <t>portable air conditioner, ac hose adapter, exhaust hose, hose reducer, dryer vent, 130mm, 150mm, hose coupler, window kit, no supports</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZXYtY2hhcmdpbmctY2FibGUtbG9jay1jb2xsYXItOC1jYWJsZS1zaXplcy0xMi10by0yNi1tbS13aXRoLXBhZGxvY2stZXllcy12aXMtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+          <t>Q3JlYXRpb24vd2FyZ2FtZS1tb3ZlbWVudC10cmF5cy0yNS0yOC01LTMyLTQwLW1tLXJvdW5kLWJhc2VzLW1hZ25ldC1yZWFkeS1tbWVyY2lhbA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EV Charging Cable Lock Collar – 8 Cable Sizes 12 to 26 mm with Padlock Eyes (Visible Deterrent) | Commercial License</t>
+          <t>Wargame Movement Trays – 25, 28.5, 32 &amp; 40 mm Round Bases (Magnet Ready)mmercial License</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5030372</t>
+          <t>https://cults3d.com/:5036277</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
         <v>9.99</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1663,34 +1663,34 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>ev charger, charging cable, cable lock, padlock, anti theft, cable clamp, electric car, home charging, wallbox, no supports</t>
+          <t>skirmish, regiment, squad, bambu, prusa, movement tray, wargame, tabletop, miniatures, 32mm base, 25mm base, 28mm, rpg, magnet, no supports, terrain, board game</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZXYtY2hhcmdpbmctY2FibGUtbG9jay1jb2xsYXItOC1jYWJsZS1zaXplcy0xMi10by0yNi1tbS13aXRoLXBhZGxvY2stZXllcy12aXM</t>
+          <t>Q3JlYXRpb24vYmFuZGVqYXMtZGUtbW92aW1pZW50by1wYXJhLWp1ZWdvcy1kZS1ndWVycmEtYmFzZXMtcmVkb25kYXMtZGUtMjUtMjgtNS0zMi15LTQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EV Charging Cable Lock Collar – 8 Cable Sizes 12 to 26 mm with Padlock Eyes (Visible Deterrent)</t>
+          <t>Wargame Movement Trays – 25, 28.5, 32 &amp; 40 mm Round Bases (Magnet Ready)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5030358</t>
+          <t>https://cults3d.com/:5036276</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
         <v>2.8</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1722,34 +1722,34 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>ev charger, charging cable, cable lock, padlock, anti theft, cable clamp, electric car, home charging, wallbox, no supports</t>
+          <t>movement tray, wargame, tabletop, miniatures, 32mm base, 25mm base, 28mm, rpg, magnet, no supports, terrain, board game</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZGVzay1zaWRlLXBvY2tldC1vcmdhbml6ZXItc2V0LXBob25lLXBlbnMtcmVtb3RlLWFuZC1rZXlzLWFkaGVzaXZlLXRhcGUtb3ItYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+          <t>Q3JlYXRpb24vY2FyLWN1cC1ob2xkZXItb3JnYW5pemVyLWluc2VydC1jb2lucy1jYXJkcy1hbmQtcGVucy02LXNpemVzLTY2LXRvLTgxLW1tLW1lLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Desk Side Pocket Organizer Set – Phone, Pens, Remote and Keys (Adhesive Tape or Screw Mount) | Commercial License</t>
+          <t>Car Cup Holder Organizer Insert – Coins, Cards and Pens, 6 Sizes 66 to 81 mm (Measure First) | Commercial License</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5024166</t>
+          <t>https://cults3d.com/:5031209</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
         <v>9.99</v>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1781,34 +1781,34 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>under desk organizer, desk organizer, wall pocket, phone holder, pen holder, remote holder, adhesive mount, desk accessory, cable organizer, no supports</t>
+          <t>car organizer, cup holder, car accessories, coin holder, card holder, pen holder, car console, interior organizer, cup holder insert, no supports</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZGVzay1zaWRlLXBvY2tldC1vcmdhbml6ZXItc2V0LXBob25lLXBlbnMtcmVtb3RlLWFuZC1rZXlzLWFkaGVzaXZlLXRhcGUtb3I</t>
+          <t>Q3JlYXRpb24vY2FyLWN1cC1ob2xkZXItb3JnYW5pemVyLWluc2VydC1jb2lucy1jYXJkcy1hbmQtcGVucy02LXNpemVzLTY2LXRvLTgxLW1tLW1l</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Desk Side Pocket Organizer Set – Phone, Pens, Remote and Keys (Adhesive Tape or Screw Mount)</t>
+          <t>Car Cup Holder Organizer Insert – Coins, Cards and Pens, 6 Sizes 66 to 81 mm (Measure First)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5024165</t>
+          <t>https://cults3d.com/:5031208</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>2.8</v>
+        <v>3.36</v>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1836,38 +1836,38 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>3.36</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>under desk organizer, desk organizer, wall pocket, phone holder, pen holder, remote holder, adhesive mount, desk accessory, cable organizer, no supports</t>
+          <t>car organizer, cup holder, car accessories, coin holder, card holder, pen holder, car console, interior organizer, cup holder insert, no supports</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vdHdpc3RlZC1mYWNldGVkLXBsYW50ZXItZm9yLTktMTItMTUtY20tbnVyc2VyeS1wb3RzLWRyYWluYWdlLXNhdWNlci1jb20</t>
+          <t>Q3JlYXRpb24vY29ybmVyLWJyYWNrZXQtd2l0aC1zaWRlLWd1c3NldHMtY291bnRlcnN1bmstbTMtbTQtbTUtNDAtdG8tMTAwLW1tLWNvbW1lcmM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Twisted Faceted Planter for 9, 12 &amp; 15 cm Nursery Pots – Drainage + Saucer | Commercial License</t>
+          <t>Corner Bracket with Side Gussets – Countersunk, M3/M4/M5, 40 to 100 mm | Commercial License</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020606</t>
+          <t>https://cults3d.com/:5030842</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
         <v>9.99</v>
       </c>
       <c r="F23" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1899,34 +1899,34 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>home, planter, plant pot, succulent pot, flower pot, home decor, modern, geometric, drainage, saucer, no supports</t>
+          <t>bracket, corner bracket, angle bracket, shelf bracket, gusset, hardware, woodworking, diy, workshop, countersunk, maker</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vdHdpc3RlZC1mYWNldGVkLXBsYW50ZXItZm9yLTktMTItMTUtY20tbnVyc2VyeS1wb3RzLWRyYWluYWdlLXNhdWNlcg</t>
+          <t>Q3JlYXRpb24vY29ybmVyLWJyYWNrZXQtd2l0aC1zaWRlLWd1c3NldHMtY291bnRlcnN1bmstbTMtbTQtbTUtNDAtdG8tMTAwLW1t</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Twisted Faceted Planter for 9, 12 &amp; 15 cm Nursery Pots – Drainage + Saucer</t>
+          <t>Corner Bracket with Side Gussets – Countersunk, M3/M4/M5, 40 to 100 mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5020604</t>
+          <t>https://cults3d.com/:5030841</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>2.83</v>
+        <v>1.67</v>
       </c>
       <c r="F24" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1954,38 +1954,38 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.83</v>
+        <v>1.67</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>home, planter, plant pot, succulent pot, flower pot, home decor, modern, geometric, drainage, saucer, no supports</t>
+          <t>bracket, corner bracket, angle bracket, shelf bracket, gusset, hardware, woodworking, diy, workshop, countersunk, maker</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZGVzay1vcmdhbml6ZXItY2FkZHktcGVuLWN1cHMtcGhvbmUtc2xvdC1zdGlja3ktbm90ZS1wYWQtYnVzaW5lc3MtY2FyZC1ob2wtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+          <t>Q3JlYXRpb24vZXYtY2hhcmdpbmctY2FibGUtbG9jay1jb2xsYXItOC1jYWJsZS1zaXplcy0xMi10by0yNi1tbS13aXRoLXBhZGxvY2stZXllcy12aXMtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Desk Organizer Caddy – Pen Cups, Phone Slot, Sticky Note Pad &amp; Business Card Holder | Commercial License</t>
+          <t>EV Charging Cable Lock Collar – 8 Cable Sizes 12 to 26 mm with Padlock Eyes (Visible Deterrent) | Commercial License</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5013777</t>
+          <t>https://cults3d.com/:5030372</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
         <v>9.99</v>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2017,34 +2017,34 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>desk organizer, pen holder, desk caddy, office, phone holder, sticky notes, business cards, desk accessory, no supports, stationery</t>
+          <t>ev charger, charging cable, cable lock, padlock, anti theft, cable clamp, electric car, home charging, wallbox, no supports</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vZGVzay1vcmdhbml6ZXItY2FkZHktcGVuLWN1cHMtcGhvbmUtc2xvdC1zdGlja3ktbm90ZS1wYWQtYnVzaW5lc3MtY2FyZC1ob2w</t>
+          <t>Q3JlYXRpb24vZXYtY2hhcmdpbmctY2FibGUtbG9jay1jb2xsYXItOC1jYWJsZS1zaXplcy0xMi10by0yNi1tbS13aXRoLXBhZGxvY2stZXllcy12aXM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Desk Organizer Caddy – Pen Cups, Phone Slot, Sticky Note Pad &amp; Business Card Holder</t>
+          <t>EV Charging Cable Lock Collar – 8 Cable Sizes 12 to 26 mm with Padlock Eyes (Visible Deterrent)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5013775</t>
+          <t>https://cults3d.com/:5030358</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
-        <v>3.37</v>
+        <v>2.8</v>
       </c>
       <c r="F26" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2072,38 +2072,38 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.37</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>desk organizer, pen holder, desk caddy, office, phone holder, sticky notes, business cards, desk accessory, no supports, stationery</t>
+          <t>ev charger, charging cable, cable lock, padlock, anti theft, cable clamp, electric car, home charging, wallbox, no supports</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vc29kYS1jYW4tbGlkLXNuYXAtb24tY292ZXItZm9yLXN0YW5kYXJkLXNsaW0tc2xlZWstY2Fucy13aXRoLXN0cmF3LWhvbGUtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+          <t>Q3JlYXRpb24vZGVzay1zaWRlLXBvY2tldC1vcmdhbml6ZXItc2V0LXBob25lLXBlbnMtcmVtb3RlLWFuZC1rZXlzLWFkaGVzaXZlLXRhcGUtb3ItYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Soda Can Lid – Snap-On Cover for Standard, Slim &amp; Sleek Cans, With Straw Hole | Commercial License</t>
+          <t>Desk Side Pocket Organizer Set – Phone, Pens, Remote and Keys (Adhesive Tape or Screw Mount) | Commercial License</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5013380</t>
+          <t>https://cults3d.com/:5024166</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
         <v>9.99</v>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2135,34 +2135,34 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>can lid, can cover, soda can, beverage cover, drink cover, can topper, straw hole, no supports, picnic, camping</t>
+          <t>under desk organizer, desk organizer, wall pocket, phone holder, pen holder, remote holder, adhesive mount, desk accessory, cable organizer, no supports</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vc29kYS1jYW4tbGlkLXNuYXAtb24tY292ZXItZm9yLXN0YW5kYXJkLXNsaW0tc2xlZWstY2Fucy13aXRoLXN0cmF3LWhvbGU</t>
+          <t>Q3JlYXRpb24vZGVzay1zaWRlLXBvY2tldC1vcmdhbml6ZXItc2V0LXBob25lLXBlbnMtcmVtb3RlLWFuZC1rZXlzLWFkaGVzaXZlLXRhcGUtb3I</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Soda Can Lid – Snap-On Cover for Standard, Slim &amp; Sleek Cans, With Straw Hole</t>
+          <t>Desk Side Pocket Organizer Set – Phone, Pens, Remote and Keys (Adhesive Tape or Screw Mount)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5013379</t>
+          <t>https://cults3d.com/:5024165</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E28" t="n">
-        <v>1.68</v>
+        <v>2.8</v>
       </c>
       <c r="F28" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2190,38 +2190,38 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.68</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>can lid, can cover, soda can, beverage cover, drink cover, can topper, straw hole, no supports, picnic, camping</t>
+          <t>under desk organizer, desk organizer, wall pocket, phone holder, pen holder, remote holder, adhesive mount, desk accessory, cable organizer, no supports</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcGhvbmUtdGFibGV0LXN0YW5kLTMtdmlld2luZy1hbmdsZXMtY2FibGUtc2xvdC10aGljay1jYXNlLXZlcnNpb24tY29tbWVy</t>
+          <t>Q3JlYXRpb24vdHdpc3RlZC1mYWNldGVkLXBsYW50ZXItZm9yLTktMTItMTUtY20tbnVyc2VyeS1wb3RzLWRyYWluYWdlLXNhdWNlci1jb20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Phone &amp; Tablet Stand – 3 Viewing Angles, Cable Slot, Thick Case Version | Commercial License</t>
+          <t>Twisted Faceted Planter for 9, 12 &amp; 15 cm Nursery Pots – Drainage + Saucer | Commercial License</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5013062</t>
+          <t>https://cults3d.com/:5020606</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
         <v>9.99</v>
       </c>
       <c r="F29" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2253,34 +2253,34 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>accessory, phone stand, phone holder, tablet stand, desk setup, office, smartphone, charging stand, minimalist, no supports, desk accessory</t>
+          <t>home, planter, plant pot, succulent pot, flower pot, home decor, modern, geometric, drainage, saucer, no supports</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcGhvbmUtdGFibGV0LXN0YW5kLTMtdmlld2luZy1hbmdsZXMtY2FibGUtc2xvdC10aGljay1jYXNlLXZlcnNpb24</t>
+          <t>Q3JlYXRpb24vdHdpc3RlZC1mYWNldGVkLXBsYW50ZXItZm9yLTktMTItMTUtY20tbnVyc2VyeS1wb3RzLWRyYWluYWdlLXNhdWNlcg</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Phone &amp; Tablet Stand – 3 Viewing Angles, Cable Slot, Thick Case Version</t>
+          <t>Twisted Faceted Planter for 9, 12 &amp; 15 cm Nursery Pots – Drainage + Saucer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5013059</t>
+          <t>https://cults3d.com/:5020604</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>2.51</v>
+        <v>2.82</v>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2308,38 +2308,38 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.51</v>
+        <v>2.82</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>accessory, phone stand, phone holder, tablet stand, desk setup, office, smartphone, charging stand, minimalist, no supports, desk accessory</t>
+          <t>home, planter, plant pot, succulent pot, flower pot, home decor, modern, geometric, drainage, saucer, no supports</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vbWluaW1hbC1oZWFkcGhvbmUtc3RhbmQtMjMwLW1tLWNvbXBhY3QtcHJpbnRzLWZsYXQtbm8tc3VwcG9ydHMtY29tbWVyY2lh</t>
+          <t>Q3JlYXRpb24vZGVzay1vcmdhbml6ZXItY2FkZHktcGVuLWN1cHMtcGhvbmUtc2xvdC1zdGlja3ktbm90ZS1wYWQtYnVzaW5lc3MtY2FyZC1ob2wtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Minimal Headphone Stand – 230 mm &amp; Compact, Prints Flat, No Supports | Commercial License</t>
+          <t>Desk Organizer Caddy – Pen Cups, Phone Slot, Sticky Note Pad &amp; Business Card Holder | Commercial License</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5012946</t>
+          <t>https://cults3d.com/:5013777</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
         <v>9.99</v>
       </c>
       <c r="F31" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2371,34 +2371,34 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>headphone stand, headset holder, gaming, desk setup, minimalist, headphones, stand, no supports, gamer, office</t>
+          <t>desk organizer, pen holder, desk caddy, office, phone holder, sticky notes, business cards, desk accessory, no supports, stationery</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vbWluaW1hbC1oZWFkcGhvbmUtc3RhbmQtMjMwLW1tLWNvbXBhY3QtcHJpbnRzLWZsYXQtbm8tc3VwcG9ydHMtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+          <t>Q3JlYXRpb24vZGVzay1vcmdhbml6ZXItY2FkZHktcGVuLWN1cHMtcGhvbmUtc2xvdC1zdGlja3ktbm90ZS1wYWQtYnVzaW5lc3MtY2FyZC1ob2w</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Minimal Headphone Stand – 230 mm &amp; Compact, Prints Flat, No Supports</t>
+          <t>Desk Organizer Caddy – Pen Cups, Phone Slot, Sticky Note Pad &amp; Business Card Holder</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5012943</t>
+          <t>https://cults3d.com/:5013775</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E32" t="n">
-        <v>1.99</v>
+        <v>3.36</v>
       </c>
       <c r="F32" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2426,38 +2426,38 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.99</v>
+        <v>3.36</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>headphone stand, headset holder, gaming, desk setup, minimalist, headphones, stand, no supports, gamer, office</t>
+          <t>desk organizer, pen holder, desk caddy, office, phone holder, sticky notes, business cards, desk accessory, no supports, stationery</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vaGV4LWRlc2stb3JnYW5pemVyLW1vZHVsYXItaG9uZXljb21iLXBlbi1ob2xkZXItMS0zLTUtNy1jZWxscy1jb21tZXJjaQ</t>
+          <t>Q3JlYXRpb24vc29kYS1jYW4tbGlkLXNuYXAtb24tY292ZXItZm9yLXN0YW5kYXJkLXNsaW0tc2xlZWstY2Fucy13aXRoLXN0cmF3LWhvbGUtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hex Desk Organizer – Modular Honeycomb Pen Holder (1, 3, 5 &amp; 7 cells) | Commercial License</t>
+          <t>Soda Can Lid – Snap-On Cover for Standard, Slim &amp; Sleek Cans, With Straw Hole | Commercial License</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5012782</t>
+          <t>https://cults3d.com/:5013380</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E33" t="n">
         <v>9.99</v>
       </c>
       <c r="F33" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2489,34 +2489,34 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>desk organizer, pen holder, honeycomb, hexagon, office, storage, minimalist, desk, organizer, no supports</t>
+          <t>can lid, can cover, soda can, beverage cover, drink cover, can topper, straw hole, no supports, picnic, camping</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vaGV4LWRlc2stb3JnYW5pemVyLW1vZHVsYXItaG9uZXljb21iLXBlbi1ob2xkZXItMS0zLTUtNy1jZWxscw</t>
+          <t>Q3JlYXRpb24vc29kYS1jYW4tbGlkLXNuYXAtb24tY292ZXItZm9yLXN0YW5kYXJkLXNsaW0tc2xlZWstY2Fucy13aXRoLXN0cmF3LWhvbGU</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hex Desk Organizer – Modular Honeycomb Pen Holder (1, 3, 5 &amp; 7 cells)</t>
+          <t>Soda Can Lid – Snap-On Cover for Standard, Slim &amp; Sleek Cans, With Straw Hole</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5012781</t>
+          <t>https://cults3d.com/:5013379</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E34" t="n">
-        <v>2.49</v>
+        <v>1.67</v>
       </c>
       <c r="F34" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2544,38 +2544,38 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.49</v>
+        <v>1.67</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>desk organizer, pen holder, honeycomb, hexagon, office, storage, minimalist, desk, organizer, no supports</t>
+          <t>can lid, can cover, soda can, beverage cover, drink cover, can topper, straw hole, no supports, picnic, camping</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbi1jb21tZXJjaWFsLWxpLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
+          <t>Q3JlYXRpb24vcGhvbmUtdGFibGV0LXN0YW5kLTMtdmlld2luZy1hbmdsZXMtY2FibGUtc2xvdC10aGljay1jYXNlLXZlcnNpb24tY29tbWVy</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween) | Commercial License</t>
+          <t>Phone &amp; Tablet Stand – 3 Viewing Angles, Cable Slot, Thick Case Version | Commercial License</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5012593</t>
+          <t>https://cults3d.com/:5013062</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E35" t="n">
         <v>9.99</v>
       </c>
       <c r="F35" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2607,35 +2607,35 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+          <t>accessory, phone stand, phone holder, tablet stand, desk setup, office, smartphone, charging stand, minimalist, no supports, desk accessory</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbi1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
+          <t>Q3JlYXRpb24vcGhvbmUtdGFibGV0LXN0YW5kLTMtdmlld2luZy1hbmdsZXMtY2FibGUtc2xvdC10aGljay1jYXNlLXZlcnNpb24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween)</t>
+          <t>Phone &amp; Tablet Stand – 3 Viewing Angles, Cable Slot, Thick Case Version</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5012591</t>
+          <t>https://cults3d.com/:5013059</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>18</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="F36" t="n">
         <v>13</v>
       </c>
-      <c r="E36" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="F36" t="n">
-        <v>33</v>
-      </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
@@ -2662,38 +2662,38 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.49</v>
+        <v>2.51</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+          <t>accessory, phone stand, phone holder, tablet stand, desk setup, office, smartphone, charging stand, minimalist, no supports, desk accessory</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbg</t>
+          <t>Q3JlYXRpb24vbWluaW1hbC1oZWFkcGhvbmUtc3RhbmQtMjMwLW1tLWNvbXBhY3QtcHJpbnRzLWZsYXQtbm8tc3VwcG9ydHMtY29tbWVyY2lh</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween)</t>
+          <t>Minimal Headphone Stand – 230 mm &amp; Compact, Prints Flat, No Supports | Commercial License</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://cults3d.com/:5004161</t>
+          <t>https://cults3d.com/:5012946</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E37" t="n">
-        <v>1.49</v>
+        <v>9.99</v>
       </c>
       <c r="F37" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2721,68 +2721,422 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.49</v>
+        <v>9.99</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+          <t>headphone stand, headset holder, gaming, desk setup, minimalist, headphones, stand, no supports, gamer, office</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Q3JlYXRpb24vbWluaW1hbC1oZWFkcGhvbmUtc3RhbmQtMjMwLW1tLWNvbXBhY3QtcHJpbnRzLWZsYXQtbm8tc3VwcG9ydHMtYWR2YW5jZWR1cmJhbmRlc2lnbmxhYm9yYXRvcjE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Minimal Headphone Stand – 230 mm &amp; Compact, Prints Flat, No Supports</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012943</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F38" t="n">
+        <v>24</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>headphone stand, headset holder, gaming, desk setup, minimalist, headphones, stand, no supports, gamer, office</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vaGV4LWRlc2stb3JnYW5pemVyLW1vZHVsYXItaG9uZXljb21iLXBlbi1ob2xkZXItMS0zLTUtNy1jZWxscy1jb21tZXJjaQ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hex Desk Organizer – Modular Honeycomb Pen Holder (1, 3, 5 &amp; 7 cells) | Commercial License</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012782</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>18</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F39" t="n">
+        <v>40</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>desk organizer, pen holder, honeycomb, hexagon, office, storage, minimalist, desk, organizer, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vaGV4LWRlc2stb3JnYW5pemVyLW1vZHVsYXItaG9uZXljb21iLXBlbi1ob2xkZXItMS0zLTUtNy1jZWxscw</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hex Desk Organizer – Modular Honeycomb Pen Holder (1, 3, 5 &amp; 7 cells)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012781</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>18</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="F40" t="n">
+        <v>30</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>desk organizer, pen holder, honeycomb, hexagon, office, storage, minimalist, desk, organizer, no supports</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbi1jb21tZXJjaWFsLWxpLWFkdmFuY2VkdXJiYW5kZXNpZ25sYWJvcmF0b3Ix</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween) | Commercial License</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012593</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>18</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F41" t="n">
+        <v>33</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbi1hZHZhbmNlZHVyYmFuZGVzaWdubGFib3JhdG9yMQ</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5012591</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>18</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F42" t="n">
+        <v>34</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Q3JlYXRpb24vcHVtcGtpbi10ZWFsaWdodC1sYW50ZXJuLTQtY2FydmVkLWZhY2VzLXN0ZW0tbGlkLWhhbGxvd2Vlbg</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pumpkin Tealight Lantern – 4 Carved Faces + Stem Lid (Halloween)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://cults3d.com/:5004161</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>20</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F43" t="n">
+        <v>28</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Esperar: todavía no hay datos suficientes</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>halloween, pumpkin, jack o lantern, halloween decor, tealight holder, lantern, spooky, led candle, autumn</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Q3JlYXRpb24vc25hcC1pbi1kZXNrLWNhYmxlLWNsaXBzLXRhcGUtbW91bnQtMS10by01LXNsb3Rz</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Snap-In Desk Cable Clips – Tape Mount, 1 to 5 Slots</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>https://cults3d.com/:5015799</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>13</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>57</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="D44" t="n">
+        <v>18</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>62</v>
+      </c>
+      <c r="G44" t="n">
         <v>1</v>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr">
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>GRATIS</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Imán de seguidores: 4 descargas</t>
         </is>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>cable management, cable clip, desk setup, cable organizer, office, usb cable, charger, tape mount, no supports, gadget</t>
         </is>
@@ -2799,7 +3153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2826,17 +3180,33 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
+        <v>46316.42730324074</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Professional Radiation Shield for Weather Stations &amp; Agro-IoT</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
         <v>46284.67179398148</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Professional Radiation Shield for Weather Stations &amp; Agro-IoT</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="n">
         <v>1.18</v>
       </c>
-      <c r="D2" t="b">
+      <c r="D3" t="b">
         <v>0</v>
       </c>
     </row>

--- a/reportes/ventas_propias.xlsx
+++ b/reportes/ventas_propias.xlsx
@@ -1159,7 +1159,7 @@
         <v>9.99</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
         <v>1.67</v>
       </c>
       <c r="F34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
